--- a/data/nzd0201/nzd0201.xlsx
+++ b/data/nzd0201/nzd0201.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G752"/>
+  <dimension ref="A1:G757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20722,6 +20722,141 @@
         <v>353.61</v>
       </c>
       <c r="G752" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>349.93</v>
+      </c>
+      <c r="C753" t="n">
+        <v>349.24</v>
+      </c>
+      <c r="D753" t="n">
+        <v>347.21</v>
+      </c>
+      <c r="E753" t="n">
+        <v>345.62</v>
+      </c>
+      <c r="F753" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>349.47</v>
+      </c>
+      <c r="C754" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="D754" t="n">
+        <v>346.23</v>
+      </c>
+      <c r="E754" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="F754" t="n">
+        <v>352.35</v>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:16+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>348.49</v>
+      </c>
+      <c r="C755" t="n">
+        <v>347.05</v>
+      </c>
+      <c r="D755" t="n">
+        <v>344.54</v>
+      </c>
+      <c r="E755" t="n">
+        <v>342.17</v>
+      </c>
+      <c r="F755" t="n">
+        <v>349.87</v>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="C756" t="n">
+        <v>348.03</v>
+      </c>
+      <c r="D756" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="E756" t="n">
+        <v>342.68</v>
+      </c>
+      <c r="F756" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>348.81</v>
+      </c>
+      <c r="C757" t="n">
+        <v>348.37</v>
+      </c>
+      <c r="D757" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="E757" t="n">
+        <v>343.11</v>
+      </c>
+      <c r="F757" t="n">
+        <v>351.25</v>
+      </c>
+      <c r="G757" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20738,7 +20873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B783"/>
+  <dimension ref="A1:B790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28571,6 +28706,76 @@
       </c>
       <c r="B783" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-06-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B784" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B785" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-07-05 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B786" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B787" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B788" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B789" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B790" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -28739,28 +28944,28 @@
         <v>0.0586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01026826163811108</v>
+        <v>0.007317833414803476</v>
       </c>
       <c r="J2" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K2" t="n">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003855155440054547</v>
+        <v>0.0001983084829447757</v>
       </c>
       <c r="M2" t="n">
-        <v>2.897951767754993</v>
+        <v>2.889696906833032</v>
       </c>
       <c r="N2" t="n">
-        <v>14.80510375929022</v>
+        <v>14.74149541195487</v>
       </c>
       <c r="O2" t="n">
-        <v>3.847740084684804</v>
+        <v>3.839465511233936</v>
       </c>
       <c r="P2" t="n">
-        <v>350.9077983182512</v>
+        <v>350.9397381684912</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28817,28 +29022,28 @@
         <v>0.055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03873181875440462</v>
+        <v>0.03086800797306456</v>
       </c>
       <c r="J3" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K3" t="n">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004455923545781393</v>
+        <v>0.002841134442503779</v>
       </c>
       <c r="M3" t="n">
-        <v>3.40185338497491</v>
+        <v>3.410702238170573</v>
       </c>
       <c r="N3" t="n">
-        <v>18.15637262878476</v>
+        <v>18.26486170945548</v>
       </c>
       <c r="O3" t="n">
-        <v>4.261029526861409</v>
+        <v>4.273740950204572</v>
       </c>
       <c r="P3" t="n">
-        <v>353.1436381809562</v>
+        <v>353.2288610165014</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28895,28 +29100,28 @@
         <v>0.1052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1251649042037688</v>
+        <v>0.1180864840927907</v>
       </c>
       <c r="J4" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K4" t="n">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03185581408253302</v>
+        <v>0.02866307486579245</v>
       </c>
       <c r="M4" t="n">
-        <v>4.154995907931923</v>
+        <v>4.1620437753799</v>
       </c>
       <c r="N4" t="n">
-        <v>25.79211875725865</v>
+        <v>25.80917461317117</v>
       </c>
       <c r="O4" t="n">
-        <v>5.078594171348864</v>
+        <v>5.080273084507483</v>
       </c>
       <c r="P4" t="n">
-        <v>347.6389946121758</v>
+        <v>347.7157134560546</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28973,28 +29178,28 @@
         <v>0.1131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2885091950573918</v>
+        <v>0.2751210669293918</v>
       </c>
       <c r="J5" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K5" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1158771267548429</v>
+        <v>0.106075613140117</v>
       </c>
       <c r="M5" t="n">
-        <v>4.78807746691098</v>
+        <v>4.837159897353341</v>
       </c>
       <c r="N5" t="n">
-        <v>34.38891135150721</v>
+        <v>34.82579204458266</v>
       </c>
       <c r="O5" t="n">
-        <v>5.864205943817732</v>
+        <v>5.901338157111712</v>
       </c>
       <c r="P5" t="n">
-        <v>346.0333653473993</v>
+        <v>346.1782119873936</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29051,28 +29256,28 @@
         <v>0.1158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2268704040926209</v>
+        <v>0.2147876371716465</v>
       </c>
       <c r="J6" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K6" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08154557798911899</v>
+        <v>0.073560031347223</v>
       </c>
       <c r="M6" t="n">
-        <v>4.610788532839531</v>
+        <v>4.650532292721842</v>
       </c>
       <c r="N6" t="n">
-        <v>31.3904169555855</v>
+        <v>31.72210602213863</v>
       </c>
       <c r="O6" t="n">
-        <v>5.602715141392207</v>
+        <v>5.632238100625596</v>
       </c>
       <c r="P6" t="n">
-        <v>354.3854041528136</v>
+        <v>354.5161238748678</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29110,7 +29315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G752"/>
+  <dimension ref="A1:G757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56901,6 +57106,191 @@
         </is>
       </c>
     </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>-37.35958922626422,175.9379901237097</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>-37.36029717930854,175.93786635456217</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>-37.36100705859977,175.93773895574125</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>-37.36172129419309,175.9376508548719</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>-37.36243723631596,175.93768077079034</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>-37.3595887762864,175.937984964252</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>-37.36029675672685,175.93786119142098</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>-37.36100638579461,175.93772793040145</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>-37.36172104255438,175.93764420520336</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>-37.36243704643024,175.93767445657124</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:16+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>-37.35958781763729,175.93797397236392</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>-37.360295167450175,175.93784177352094</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>-37.36100522554651,175.9377089173157</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>-37.36171982274103,175.9376119712171</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>-37.36243620550373,175.9376464936012</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>-37.359587494826634,175.93797027101394</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>-37.36029606773446,175.93785277325614</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>-37.36100585029587,175.93771915513105</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>-37.36172004026084,175.93761771923562</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>-37.36243646659855,175.93765517565237</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>-37.35958813066569,175.93797756155186</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>-37.36029638007775,175.93785658949088</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>-37.36100556195013,175.93771442998548</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>-37.36172022365969,175.93762256560416</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>-37.36243667343946,175.937662053641</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0201/nzd0201.xlsx
+++ b/data/nzd0201/nzd0201.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G757"/>
+  <dimension ref="A1:G761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20857,6 +20857,114 @@
         <v>351.25</v>
       </c>
       <c r="G757" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:27+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>348.7</v>
+      </c>
+      <c r="C758" t="n">
+        <v>348.34</v>
+      </c>
+      <c r="D758" t="n">
+        <v>345.36</v>
+      </c>
+      <c r="E758" t="n">
+        <v>343.22</v>
+      </c>
+      <c r="F758" t="n">
+        <v>351.53</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>350.01</v>
+      </c>
+      <c r="C759" t="n">
+        <v>349.24</v>
+      </c>
+      <c r="D759" t="n">
+        <v>346.28</v>
+      </c>
+      <c r="E759" t="n">
+        <v>344.38</v>
+      </c>
+      <c r="F759" t="n">
+        <v>352.44</v>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="C760" t="n">
+        <v>350.07</v>
+      </c>
+      <c r="D760" t="n">
+        <v>346.95</v>
+      </c>
+      <c r="E760" t="n">
+        <v>345.21</v>
+      </c>
+      <c r="F760" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>350.92</v>
+      </c>
+      <c r="C761" t="n">
+        <v>350.25</v>
+      </c>
+      <c r="D761" t="n">
+        <v>346.76</v>
+      </c>
+      <c r="E761" t="n">
+        <v>345.23</v>
+      </c>
+      <c r="F761" t="n">
+        <v>352.98</v>
+      </c>
+      <c r="G761" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20873,7 +20981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B790"/>
+  <dimension ref="A1:B794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28776,6 +28884,46 @@
       </c>
       <c r="B790" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B791" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B792" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B793" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B794" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -28944,28 +29092,28 @@
         <v>0.0586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007317833414803476</v>
+        <v>0.006292030963583322</v>
       </c>
       <c r="J2" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="K2" t="n">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001983084829447757</v>
+        <v>0.0001482556841930771</v>
       </c>
       <c r="M2" t="n">
-        <v>2.889696906833032</v>
+        <v>2.878289528081861</v>
       </c>
       <c r="N2" t="n">
-        <v>14.74149541195487</v>
+        <v>14.67327475026858</v>
       </c>
       <c r="O2" t="n">
-        <v>3.839465511233936</v>
+        <v>3.830571073647973</v>
       </c>
       <c r="P2" t="n">
-        <v>350.9397381684912</v>
+        <v>350.9508656042252</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29022,28 +29170,28 @@
         <v>0.055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03086800797306456</v>
+        <v>0.02602378634681232</v>
       </c>
       <c r="J3" t="n">
+        <v>760</v>
+      </c>
+      <c r="K3" t="n">
         <v>756</v>
       </c>
-      <c r="K3" t="n">
-        <v>752</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.002841134442503779</v>
+        <v>0.002032345298761284</v>
       </c>
       <c r="M3" t="n">
-        <v>3.410702238170573</v>
+        <v>3.412043165179429</v>
       </c>
       <c r="N3" t="n">
-        <v>18.26486170945548</v>
+        <v>18.28046422757694</v>
       </c>
       <c r="O3" t="n">
-        <v>4.273740950204572</v>
+        <v>4.27556595406701</v>
       </c>
       <c r="P3" t="n">
-        <v>353.2288610165014</v>
+        <v>353.2815143903956</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29100,28 +29248,28 @@
         <v>0.1052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1180864840927907</v>
+        <v>0.1132754131549797</v>
       </c>
       <c r="J4" t="n">
+        <v>760</v>
+      </c>
+      <c r="K4" t="n">
         <v>756</v>
       </c>
-      <c r="K4" t="n">
-        <v>752</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.02866307486579245</v>
+        <v>0.02662906564587875</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1620437753799</v>
+        <v>4.163479112384443</v>
       </c>
       <c r="N4" t="n">
-        <v>25.80917461317117</v>
+        <v>25.78226320368635</v>
       </c>
       <c r="O4" t="n">
-        <v>5.080273084507483</v>
+        <v>5.077623775319155</v>
       </c>
       <c r="P4" t="n">
-        <v>347.7157134560546</v>
+        <v>347.7680096701554</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29178,28 +29326,28 @@
         <v>0.1131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2751210669293918</v>
+        <v>0.2655556189773813</v>
       </c>
       <c r="J5" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="K5" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L5" t="n">
-        <v>0.106075613140117</v>
+        <v>0.09950392630918137</v>
       </c>
       <c r="M5" t="n">
-        <v>4.837159897353341</v>
+        <v>4.869291487602027</v>
       </c>
       <c r="N5" t="n">
-        <v>34.82579204458266</v>
+        <v>35.07060651404878</v>
       </c>
       <c r="O5" t="n">
-        <v>5.901338157111712</v>
+        <v>5.922044116185624</v>
       </c>
       <c r="P5" t="n">
-        <v>346.1782119873936</v>
+        <v>346.2820075680042</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29256,28 +29404,28 @@
         <v>0.1158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2147876371716465</v>
+        <v>0.2065787094736275</v>
       </c>
       <c r="J6" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="K6" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L6" t="n">
-        <v>0.073560031347223</v>
+        <v>0.06854034922494079</v>
       </c>
       <c r="M6" t="n">
-        <v>4.650532292721842</v>
+        <v>4.674616144357725</v>
       </c>
       <c r="N6" t="n">
-        <v>31.72210602213863</v>
+        <v>31.86981440329572</v>
       </c>
       <c r="O6" t="n">
-        <v>5.632238100625596</v>
+        <v>5.645335632475337</v>
       </c>
       <c r="P6" t="n">
-        <v>354.5161238748678</v>
+        <v>354.6052012360935</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29315,7 +29463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G757"/>
+  <dimension ref="A1:G761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57291,6 +57439,154 @@
         </is>
       </c>
     </row>
+    <row r="758">
+      <c r="A758" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:27+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>-37.359588023062194,175.9379763277685</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>-37.36029635251806,175.93785625276428</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>-37.36100578850751,175.93771814259986</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>-37.36172027057563,175.93762380537285</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>-37.36243676838269,175.9376652107505</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>-37.359589304521194,175.9379910210067</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>-37.36029717930854,175.93786635456217</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>-37.361006420121434,175.93772849291878</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>-37.36172076532486,175.93763687929734</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>-37.36243707694761,175.9376754713565</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>-37.359590292515044,175.93800234938143</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>-37.360297941792325,175.93787567066477</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>-37.361006880100554,175.93773603065108</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>-37.36172111932555,175.9376462339158</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>-37.362437300741384,175.93768291311468</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>-37.359590194693915,175.93800122776017</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>-37.360298107150165,175.9378776910244</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>-37.36100674965876,175.93773389308518</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>-37.361721127855695,175.93764645932828</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>-37.362437260051635,175.93768156006772</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0201/nzd0201.xlsx
+++ b/data/nzd0201/nzd0201.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G761"/>
+  <dimension ref="A1:G764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20965,6 +20965,87 @@
         <v>352.98</v>
       </c>
       <c r="G761" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>351.21</v>
+      </c>
+      <c r="C762" t="n">
+        <v>350.68</v>
+      </c>
+      <c r="D762" t="n">
+        <v>345.88</v>
+      </c>
+      <c r="E762" t="n">
+        <v>344.39</v>
+      </c>
+      <c r="F762" t="n">
+        <v>352.61</v>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>350.88</v>
+      </c>
+      <c r="C763" t="n">
+        <v>349.94</v>
+      </c>
+      <c r="D763" t="n">
+        <v>346.4</v>
+      </c>
+      <c r="E763" t="n">
+        <v>343.96</v>
+      </c>
+      <c r="F763" t="n">
+        <v>352.58</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>351.52</v>
+      </c>
+      <c r="C764" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="D764" t="n">
+        <v>346.71</v>
+      </c>
+      <c r="E764" t="n">
+        <v>344.36</v>
+      </c>
+      <c r="F764" t="n">
+        <v>353.03</v>
+      </c>
+      <c r="G764" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20981,7 +21062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B794"/>
+  <dimension ref="A1:B797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28924,6 +29005,36 @@
       </c>
       <c r="B794" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B795" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B796" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B797" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -29092,28 +29203,28 @@
         <v>0.0586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006292030963583322</v>
+        <v>0.006355291941133649</v>
       </c>
       <c r="J2" t="n">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="K2" t="n">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001482556841930771</v>
+        <v>0.0001525870921171846</v>
       </c>
       <c r="M2" t="n">
-        <v>2.878289528081861</v>
+        <v>2.867993891136457</v>
       </c>
       <c r="N2" t="n">
-        <v>14.67327475026858</v>
+        <v>14.61579981462224</v>
       </c>
       <c r="O2" t="n">
-        <v>3.830571073647973</v>
+        <v>3.823061576096079</v>
       </c>
       <c r="P2" t="n">
-        <v>350.9508656042252</v>
+        <v>350.9501750814488</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29170,28 +29281,28 @@
         <v>0.055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02602378634681232</v>
+        <v>0.02320742712201411</v>
       </c>
       <c r="J3" t="n">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="K3" t="n">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002032345298761284</v>
+        <v>0.00162673986712214</v>
       </c>
       <c r="M3" t="n">
-        <v>3.412043165179429</v>
+        <v>3.409673479166107</v>
       </c>
       <c r="N3" t="n">
-        <v>18.28046422757694</v>
+        <v>18.25822066840756</v>
       </c>
       <c r="O3" t="n">
-        <v>4.27556595406701</v>
+        <v>4.272963920794038</v>
       </c>
       <c r="P3" t="n">
-        <v>353.2815143903956</v>
+        <v>353.3122572669521</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29248,28 +29359,28 @@
         <v>0.1052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1132754131549797</v>
+        <v>0.1097248033158094</v>
       </c>
       <c r="J4" t="n">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="K4" t="n">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02662906564587875</v>
+        <v>0.02516693781293455</v>
       </c>
       <c r="M4" t="n">
-        <v>4.163479112384443</v>
+        <v>4.164436535724866</v>
       </c>
       <c r="N4" t="n">
-        <v>25.78226320368635</v>
+        <v>25.75960070985344</v>
       </c>
       <c r="O4" t="n">
-        <v>5.077623775319155</v>
+        <v>5.075391680437426</v>
       </c>
       <c r="P4" t="n">
-        <v>347.7680096701554</v>
+        <v>347.8067654316982</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29326,28 +29437,28 @@
         <v>0.1131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2655556189773813</v>
+        <v>0.2582941942794781</v>
       </c>
       <c r="J5" t="n">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="K5" t="n">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09950392630918137</v>
+        <v>0.0945971608069941</v>
       </c>
       <c r="M5" t="n">
-        <v>4.869291487602027</v>
+        <v>4.894080553356878</v>
       </c>
       <c r="N5" t="n">
-        <v>35.07060651404878</v>
+        <v>35.26162322042484</v>
       </c>
       <c r="O5" t="n">
-        <v>5.922044116185624</v>
+        <v>5.938149814582387</v>
       </c>
       <c r="P5" t="n">
-        <v>346.2820075680042</v>
+        <v>346.3611306721899</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29404,28 +29515,28 @@
         <v>0.1158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2065787094736275</v>
+        <v>0.2007101702058668</v>
       </c>
       <c r="J6" t="n">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="K6" t="n">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06854034922494079</v>
+        <v>0.06507665774771876</v>
       </c>
       <c r="M6" t="n">
-        <v>4.674616144357725</v>
+        <v>4.690934326109143</v>
       </c>
       <c r="N6" t="n">
-        <v>31.86981440329572</v>
+        <v>31.95941216409665</v>
       </c>
       <c r="O6" t="n">
-        <v>5.645335632475337</v>
+        <v>5.653265619453649</v>
       </c>
       <c r="P6" t="n">
-        <v>354.6052012360935</v>
+        <v>354.6691458319869</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29463,7 +29574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G761"/>
+  <dimension ref="A1:G764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57587,6 +57698,117 @@
         </is>
       </c>
     </row>
+    <row r="762">
+      <c r="A762" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>-37.359590478375154,175.93800448046187</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>-37.3602985021715,175.93788251743908</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>-37.36100614550679,175.9377239927801</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>-37.36172076958993,175.9376369920036</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>-37.36243713459151,175.93767738817297</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>-37.359590155565456,175.93800077911166</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>-37.36029782236721,175.93787421151617</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>-37.361006502505774,175.93772984296038</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>-37.36172058619169,175.93763214563504</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>-37.36243712441905,175.93767704991126</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>-37.35959078162051,175.93800795748786</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>-37.36029846542534,175.9378820684703</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>-37.36100671533196,175.93773333056785</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>-37.361720756794696,175.93763665388485</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>-37.3624372770057,175.93768212383728</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
